--- a/Input/SciGrid_IGGIELGNC_1/02_Input_and_Configuration.xlsx
+++ b/Input/SciGrid_IGGIELGNC_1/02_Input_and_Configuration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantschnig\Desktop\QGas\Input\SciGrid_IGGIELGNC_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Desktop\QGas\Input\SciGrid_IGGIELGNC_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DA237B-5EE9-4CC7-91DA-ED227E7130FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157A5F4A-CC45-4161-A298-2470EFC968E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="1220" windowWidth="28800" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input_Files" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Filename</t>
   </si>
@@ -45,67 +45,70 @@
     <t>Type</t>
   </si>
   <si>
-    <t>B_Borderpoints.geojson</t>
-  </si>
-  <si>
     <t>Border Points</t>
   </si>
   <si>
     <t>Point</t>
   </si>
   <si>
-    <t>C_Compressors.geojson</t>
-  </si>
-  <si>
     <t>Compressors</t>
   </si>
   <si>
     <t>In-Line</t>
   </si>
   <si>
-    <t>D_Demands.geojson</t>
-  </si>
-  <si>
     <t>Demands</t>
   </si>
   <si>
-    <t>L_LNGs.geojson</t>
-  </si>
-  <si>
     <t>LNG Terminals</t>
   </si>
   <si>
-    <t>N_Nodes.geojson</t>
-  </si>
-  <si>
     <t>Nodes</t>
   </si>
   <si>
-    <t>P_Powerplants.geojson</t>
-  </si>
-  <si>
     <t>Power Plants</t>
   </si>
   <si>
-    <t>PL_Pipelines.geojson</t>
-  </si>
-  <si>
     <t>Pipelines</t>
   </si>
   <si>
     <t>Line</t>
   </si>
   <si>
-    <t>PR_Productions.geojson</t>
-  </si>
-  <si>
     <t>Productions</t>
   </si>
   <si>
-    <t>S_Storages.geojson</t>
-  </si>
-  <si>
     <t>Storages</t>
+  </si>
+  <si>
+    <t>borderpoints.geojson</t>
+  </si>
+  <si>
+    <t>compressors.geojson</t>
+  </si>
+  <si>
+    <t>demands.geojson</t>
+  </si>
+  <si>
+    <t>lngs.geojson</t>
+  </si>
+  <si>
+    <t>nodes.geojson</t>
+  </si>
+  <si>
+    <t>powerplants.geojson</t>
+  </si>
+  <si>
+    <t>pipelines.geojson</t>
+  </si>
+  <si>
+    <t>productions.geojson</t>
+  </si>
+  <si>
+    <t>storages.geojson</t>
+  </si>
+  <si>
+    <t>Node</t>
   </si>
 </sst>
 </file>
@@ -433,14 +436,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="29.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,103 +463,103 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G9" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
       <c r="G11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
